--- a/Tutorials_noted/Results/InverterNewFormulation/resultsInverter.xlsx
+++ b/Tutorials_noted/Results/InverterNewFormulation/resultsInverter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="9">
   <si>
     <t>J*</t>
   </si>
@@ -37,6 +37,12 @@
   </si>
   <si>
     <t>dens0</t>
+  </si>
+  <si>
+    <t>No binary result due to no volume constraint?</t>
+  </si>
+  <si>
+    <t>volumeCons</t>
   </si>
 </sst>
 </file>
@@ -163,6 +169,664 @@
         <a:xfrm>
           <a:off x="754380" y="1943100"/>
           <a:ext cx="4282440" cy="2156460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="1">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>121920</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>144781</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>731520</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>115317</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1027" name="Picture 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5669280" y="6545581"/>
+          <a:ext cx="10911840" cy="5274056"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="1">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>297180</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>640080</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1028" name="Picture 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1089660" y="8305800"/>
+          <a:ext cx="4305300" cy="2293620"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="1">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1029" name="Picture 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1584960" y="14813280"/>
+          <a:ext cx="2910840" cy="2324100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="1">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>33226</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>91849</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1030" name="Picture 6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4724400" y="12651946"/>
+          <a:ext cx="10637520" cy="5362143"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="1">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>45954</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1031" name="Picture 7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5135880" y="19834860"/>
+          <a:ext cx="11750040" cy="5631414"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="1">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>762000</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1032" name="Picture 8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1211580" y="21755100"/>
+          <a:ext cx="4305300" cy="2232660"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="1">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>683953</xdr:colOff>
+      <xdr:row>153</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>24066</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1033" name="Picture 9"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="683953" y="28102560"/>
+          <a:ext cx="4094993" cy="2164080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="1">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>472440</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>7586</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>436580</xdr:colOff>
+      <xdr:row>169</xdr:row>
+      <xdr:rowOff>60959</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1034" name="Picture 10"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5227320" y="26342306"/>
+          <a:ext cx="9473900" cy="4625373"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="1">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>184</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>312420</xdr:colOff>
+      <xdr:row>196</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="792480" y="33649920"/>
+          <a:ext cx="4274820" cy="2209800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="1">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>175</xdr:row>
+      <xdr:rowOff>36439</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>662940</xdr:colOff>
+      <xdr:row>203</xdr:row>
+      <xdr:rowOff>159327</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5730240" y="32040439"/>
+          <a:ext cx="10782300" cy="5243528"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="1">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>221</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>234</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="457200" y="40561260"/>
+          <a:ext cx="4320540" cy="2255520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="1">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>211</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>403860</xdr:colOff>
+      <xdr:row>241</xdr:row>
+      <xdr:rowOff>11784</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5120640" y="38618160"/>
+          <a:ext cx="11132820" cy="5467704"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="1">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>259</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>281940</xdr:colOff>
+      <xdr:row>271</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="792480" y="47365920"/>
+          <a:ext cx="4244340" cy="2194560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="1">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>586740</xdr:colOff>
+      <xdr:row>246</xdr:row>
+      <xdr:rowOff>41660</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>276</xdr:row>
+      <xdr:rowOff>56118</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5341620" y="45030140"/>
+          <a:ext cx="11490960" cy="5500858"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -467,7 +1131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="C3:D43"/>
+  <dimension ref="C3:E257"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="3" spans="3:4">
@@ -569,6 +1233,347 @@
       </c>
       <c r="D43">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="62" spans="3:3">
+      <c r="C62" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="3:4">
+      <c r="C72" t="s">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="73" spans="3:4">
+      <c r="C73" t="s">
+        <v>1</v>
+      </c>
+      <c r="D73">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="74" spans="3:4">
+      <c r="C74" t="s">
+        <v>2</v>
+      </c>
+      <c r="D74">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="75" spans="3:4">
+      <c r="C75" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="76" spans="3:4">
+      <c r="C76" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="77" spans="3:4">
+      <c r="C77" t="s">
+        <v>6</v>
+      </c>
+      <c r="D77">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="78" spans="3:4">
+      <c r="C78" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="110" spans="4:5">
+      <c r="D110" t="s">
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="111" spans="4:5">
+      <c r="D111" t="s">
+        <v>1</v>
+      </c>
+      <c r="E111">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="112" spans="4:5">
+      <c r="D112" t="s">
+        <v>2</v>
+      </c>
+      <c r="E112">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="113" spans="4:5">
+      <c r="D113" t="s">
+        <v>3</v>
+      </c>
+      <c r="E113">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="114" spans="4:5">
+      <c r="D114" t="s">
+        <v>4</v>
+      </c>
+      <c r="E114">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="115" spans="4:5">
+      <c r="D115" t="s">
+        <v>6</v>
+      </c>
+      <c r="E115">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="116" spans="4:5">
+      <c r="D116" t="s">
+        <v>8</v>
+      </c>
+      <c r="E116">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="146" spans="4:5">
+      <c r="D146" t="s">
+        <v>0</v>
+      </c>
+      <c r="E146">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="147" spans="4:5">
+      <c r="D147" t="s">
+        <v>1</v>
+      </c>
+      <c r="E147">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="148" spans="4:5">
+      <c r="D148" t="s">
+        <v>2</v>
+      </c>
+      <c r="E148">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="149" spans="4:5">
+      <c r="D149" t="s">
+        <v>3</v>
+      </c>
+      <c r="E149">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="150" spans="4:5">
+      <c r="D150" t="s">
+        <v>4</v>
+      </c>
+      <c r="E150">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="151" spans="4:5">
+      <c r="D151" t="s">
+        <v>6</v>
+      </c>
+      <c r="E151">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="152" spans="4:5">
+      <c r="D152" t="s">
+        <v>8</v>
+      </c>
+      <c r="E152">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="176" spans="4:5">
+      <c r="D176" t="s">
+        <v>0</v>
+      </c>
+      <c r="E176">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="177" spans="4:5">
+      <c r="D177" t="s">
+        <v>1</v>
+      </c>
+      <c r="E177">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="178" spans="4:5">
+      <c r="D178" t="s">
+        <v>2</v>
+      </c>
+      <c r="E178">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="179" spans="4:5">
+      <c r="D179" t="s">
+        <v>3</v>
+      </c>
+      <c r="E179">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="180" spans="4:5">
+      <c r="D180" t="s">
+        <v>4</v>
+      </c>
+      <c r="E180">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="181" spans="4:5">
+      <c r="D181" t="s">
+        <v>6</v>
+      </c>
+      <c r="E181">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="182" spans="4:5">
+      <c r="D182" t="s">
+        <v>8</v>
+      </c>
+      <c r="E182">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="214" spans="3:4">
+      <c r="C214" t="s">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="215" spans="3:4">
+      <c r="C215" t="s">
+        <v>1</v>
+      </c>
+      <c r="D215">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="216" spans="3:4">
+      <c r="C216" t="s">
+        <v>2</v>
+      </c>
+      <c r="D216">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="217" spans="3:4">
+      <c r="C217" t="s">
+        <v>3</v>
+      </c>
+      <c r="D217">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="218" spans="3:4">
+      <c r="C218" t="s">
+        <v>4</v>
+      </c>
+      <c r="D218">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="219" spans="3:4">
+      <c r="C219" t="s">
+        <v>6</v>
+      </c>
+      <c r="D219">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="220" spans="3:4">
+      <c r="C220" t="s">
+        <v>8</v>
+      </c>
+      <c r="D220">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="251" spans="3:4">
+      <c r="C251" t="s">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="252" spans="3:4">
+      <c r="C252" t="s">
+        <v>1</v>
+      </c>
+      <c r="D252">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="253" spans="3:4">
+      <c r="C253" t="s">
+        <v>2</v>
+      </c>
+      <c r="D253">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="254" spans="3:4">
+      <c r="C254" t="s">
+        <v>3</v>
+      </c>
+      <c r="D254">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="255" spans="3:4">
+      <c r="C255" t="s">
+        <v>4</v>
+      </c>
+      <c r="D255">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="256" spans="3:4">
+      <c r="C256" t="s">
+        <v>6</v>
+      </c>
+      <c r="D256">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="257" spans="3:4">
+      <c r="C257" t="s">
+        <v>8</v>
+      </c>
+      <c r="D257">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
